--- a/backend/estrutura_pdm/data/xl/dados_metas_atualizados_v2.xlsx
+++ b/backend/estrutura_pdm/data/xl/dados_metas_atualizados_v2.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29324"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E104715C-0887-4632-9987-7F66DEB07631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Temas, Planos e ODS" sheetId="2" r:id="rId1"/>
@@ -16,7 +15,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">acoes_estrategicas!$A$1:$E$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Temas, Planos e ODS'!$A$1:$O$1</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2748" uniqueCount="1464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2749" uniqueCount="1464">
   <si>
     <t>Número da Meta</t>
   </si>
@@ -4542,7 +4541,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="16">
     <font>
       <sz val="11"/>
@@ -5600,35 +5599,35 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2369B40-7046-473B-B809-8561F6CA1BF7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O133"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" style="26" customWidth="1"/>
-    <col min="2" max="2" width="22.5703125" style="26" customWidth="1"/>
-    <col min="3" max="3" width="35.140625" style="26" customWidth="1"/>
-    <col min="4" max="4" width="40.7109375" style="26" customWidth="1"/>
-    <col min="5" max="5" width="47.85546875" style="26" customWidth="1"/>
-    <col min="6" max="6" width="18.28515625" style="24" customWidth="1"/>
-    <col min="7" max="7" width="18.28515625" style="26" customWidth="1"/>
-    <col min="8" max="9" width="20.7109375" style="24" customWidth="1"/>
-    <col min="10" max="10" width="19.7109375" style="26" customWidth="1"/>
-    <col min="11" max="11" width="23.5703125" style="26" customWidth="1"/>
-    <col min="12" max="12" width="30.7109375" style="24" customWidth="1"/>
-    <col min="13" max="13" width="9.140625" style="26"/>
+    <col min="1" max="1" width="17.625" style="26" customWidth="1"/>
+    <col min="2" max="2" width="22.625" style="26" customWidth="1"/>
+    <col min="3" max="3" width="35.125" style="26" customWidth="1"/>
+    <col min="4" max="4" width="40.75" style="26" customWidth="1"/>
+    <col min="5" max="5" width="47.875" style="26" customWidth="1"/>
+    <col min="6" max="6" width="18.25" style="24" customWidth="1"/>
+    <col min="7" max="7" width="18.25" style="26" customWidth="1"/>
+    <col min="8" max="9" width="20.75" style="24" customWidth="1"/>
+    <col min="10" max="10" width="19.75" style="26" customWidth="1"/>
+    <col min="11" max="11" width="23.625" style="26" customWidth="1"/>
+    <col min="12" max="12" width="30.75" style="24" customWidth="1"/>
+    <col min="13" max="13" width="9.125" style="26"/>
     <col min="14" max="14" width="15" style="26" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="36.5703125" style="26" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="26"/>
+    <col min="15" max="15" width="36.625" style="26" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.125" style="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" ht="15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5667,7 +5666,7 @@
       </c>
       <c r="O1" s="24"/>
     </row>
-    <row r="2" spans="1:15" ht="167.25">
+    <row r="2" spans="1:15" ht="150">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -5706,7 +5705,7 @@
       </c>
       <c r="O2" s="24"/>
     </row>
-    <row r="3" spans="1:15" ht="106.5">
+    <row r="3" spans="1:15" ht="90">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -5745,7 +5744,7 @@
       </c>
       <c r="O3" s="24"/>
     </row>
-    <row r="4" spans="1:15" ht="152.25">
+    <row r="4" spans="1:15" ht="150">
       <c r="A4" s="39">
         <v>3</v>
       </c>
@@ -5782,7 +5781,7 @@
       </c>
       <c r="O4" s="24"/>
     </row>
-    <row r="5" spans="1:15" ht="76.5">
+    <row r="5" spans="1:15" ht="60">
       <c r="A5" s="39">
         <v>4</v>
       </c>
@@ -5819,7 +5818,7 @@
       </c>
       <c r="O5" s="24"/>
     </row>
-    <row r="6" spans="1:15" ht="76.5">
+    <row r="6" spans="1:15" ht="60">
       <c r="A6" s="39">
         <v>5</v>
       </c>
@@ -5856,7 +5855,7 @@
       </c>
       <c r="O6" s="24"/>
     </row>
-    <row r="7" spans="1:15" ht="76.5">
+    <row r="7" spans="1:15" ht="60">
       <c r="A7" s="39">
         <v>6</v>
       </c>
@@ -5893,7 +5892,7 @@
       </c>
       <c r="O7" s="24"/>
     </row>
-    <row r="8" spans="1:15" ht="106.5">
+    <row r="8" spans="1:15" ht="90">
       <c r="A8" s="39">
         <v>7</v>
       </c>
@@ -5930,7 +5929,7 @@
       </c>
       <c r="O8" s="24"/>
     </row>
-    <row r="9" spans="1:15" ht="183">
+    <row r="9" spans="1:15" ht="165">
       <c r="A9" s="39">
         <v>8</v>
       </c>
@@ -5965,7 +5964,7 @@
       <c r="L9" s="23"/>
       <c r="O9" s="24"/>
     </row>
-    <row r="10" spans="1:15" ht="91.5">
+    <row r="10" spans="1:15" ht="90">
       <c r="A10" s="39">
         <v>9</v>
       </c>
@@ -6000,7 +5999,7 @@
       <c r="L10" s="23"/>
       <c r="O10" s="24"/>
     </row>
-    <row r="11" spans="1:15" ht="121.5">
+    <row r="11" spans="1:15" ht="105">
       <c r="A11" s="39">
         <v>10</v>
       </c>
@@ -6035,7 +6034,7 @@
       <c r="L11" s="23"/>
       <c r="O11" s="24"/>
     </row>
-    <row r="12" spans="1:15" ht="130.5">
+    <row r="12" spans="1:15" ht="142.5">
       <c r="A12" s="39">
         <v>11</v>
       </c>
@@ -6072,7 +6071,7 @@
       <c r="L12" s="23"/>
       <c r="O12" s="24"/>
     </row>
-    <row r="13" spans="1:15" ht="121.5">
+    <row r="13" spans="1:15" ht="120">
       <c r="A13" s="39">
         <v>12</v>
       </c>
@@ -6111,7 +6110,7 @@
       </c>
       <c r="O13" s="24"/>
     </row>
-    <row r="14" spans="1:15" ht="115.5">
+    <row r="14" spans="1:15" ht="99.75">
       <c r="A14" s="39">
         <v>13</v>
       </c>
@@ -6150,7 +6149,7 @@
       </c>
       <c r="O14" s="24"/>
     </row>
-    <row r="15" spans="1:15" ht="121.5">
+    <row r="15" spans="1:15" ht="105">
       <c r="A15" s="39">
         <v>14</v>
       </c>
@@ -6185,7 +6184,7 @@
       </c>
       <c r="O15" s="24"/>
     </row>
-    <row r="16" spans="1:15" ht="183">
+    <row r="16" spans="1:15" ht="165">
       <c r="A16" s="39">
         <v>15</v>
       </c>
@@ -6224,7 +6223,7 @@
       </c>
       <c r="O16" s="24"/>
     </row>
-    <row r="17" spans="1:15" ht="244.5">
+    <row r="17" spans="1:15" ht="210">
       <c r="A17" s="39">
         <v>16</v>
       </c>
@@ -6263,7 +6262,7 @@
       </c>
       <c r="O17" s="24"/>
     </row>
-    <row r="18" spans="1:15" ht="183">
+    <row r="18" spans="1:15" ht="165">
       <c r="A18" s="39">
         <v>17</v>
       </c>
@@ -6302,7 +6301,7 @@
       </c>
       <c r="O18" s="24"/>
     </row>
-    <row r="19" spans="1:15" ht="91.5">
+    <row r="19" spans="1:15" ht="90">
       <c r="A19" s="39">
         <v>18</v>
       </c>
@@ -6341,7 +6340,7 @@
       </c>
       <c r="O19" s="24"/>
     </row>
-    <row r="20" spans="1:15" ht="167.25">
+    <row r="20" spans="1:15" ht="150">
       <c r="A20" s="39">
         <v>19</v>
       </c>
@@ -6380,7 +6379,7 @@
       </c>
       <c r="O20" s="24"/>
     </row>
-    <row r="21" spans="1:15" ht="167.25">
+    <row r="21" spans="1:15" ht="150">
       <c r="A21" s="39">
         <v>20</v>
       </c>
@@ -6419,7 +6418,7 @@
       </c>
       <c r="O21" s="24"/>
     </row>
-    <row r="22" spans="1:15" ht="152.25">
+    <row r="22" spans="1:15" ht="135">
       <c r="A22" s="39">
         <v>21</v>
       </c>
@@ -6458,7 +6457,7 @@
       </c>
       <c r="O22" s="24"/>
     </row>
-    <row r="23" spans="1:15" ht="106.5">
+    <row r="23" spans="1:15" ht="105">
       <c r="A23" s="39">
         <v>22</v>
       </c>
@@ -6497,7 +6496,7 @@
       </c>
       <c r="O23" s="24"/>
     </row>
-    <row r="24" spans="1:15" ht="115.5">
+    <row r="24" spans="1:15" ht="128.25">
       <c r="A24" s="39">
         <v>23</v>
       </c>
@@ -6536,7 +6535,7 @@
       </c>
       <c r="O24" s="24"/>
     </row>
-    <row r="25" spans="1:15" ht="91.5">
+    <row r="25" spans="1:15" ht="75">
       <c r="A25" s="39">
         <v>24</v>
       </c>
@@ -6575,7 +6574,7 @@
       </c>
       <c r="O25" s="24"/>
     </row>
-    <row r="26" spans="1:15" ht="167.25">
+    <row r="26" spans="1:15" ht="150">
       <c r="A26" s="39">
         <v>25</v>
       </c>
@@ -6614,7 +6613,7 @@
       </c>
       <c r="O26" s="24"/>
     </row>
-    <row r="27" spans="1:15" ht="76.5">
+    <row r="27" spans="1:15" ht="60">
       <c r="A27" s="39">
         <v>26</v>
       </c>
@@ -6653,7 +6652,7 @@
       </c>
       <c r="O27" s="24"/>
     </row>
-    <row r="28" spans="1:15" ht="76.5">
+    <row r="28" spans="1:15" ht="60">
       <c r="A28" s="39">
         <v>27</v>
       </c>
@@ -6692,7 +6691,7 @@
       </c>
       <c r="O28" s="24"/>
     </row>
-    <row r="29" spans="1:15" ht="76.5">
+    <row r="29" spans="1:15" ht="60">
       <c r="A29" s="39">
         <v>28</v>
       </c>
@@ -6731,7 +6730,7 @@
       </c>
       <c r="O29" s="24"/>
     </row>
-    <row r="30" spans="1:15" ht="91.5">
+    <row r="30" spans="1:15" ht="75">
       <c r="A30" s="39">
         <v>29</v>
       </c>
@@ -6770,7 +6769,7 @@
       </c>
       <c r="O30" s="24"/>
     </row>
-    <row r="31" spans="1:15" ht="60.75">
+    <row r="31" spans="1:15" ht="60">
       <c r="A31" s="39">
         <v>30</v>
       </c>
@@ -6809,7 +6808,7 @@
       </c>
       <c r="O31" s="24"/>
     </row>
-    <row r="32" spans="1:15" ht="106.5">
+    <row r="32" spans="1:15" ht="90">
       <c r="A32" s="39">
         <v>31</v>
       </c>
@@ -6848,7 +6847,7 @@
       </c>
       <c r="O32" s="24"/>
     </row>
-    <row r="33" spans="1:15" ht="106.5">
+    <row r="33" spans="1:15" ht="90">
       <c r="A33" s="39">
         <v>32</v>
       </c>
@@ -6887,7 +6886,7 @@
       </c>
       <c r="O33" s="24"/>
     </row>
-    <row r="34" spans="1:15" ht="91.5">
+    <row r="34" spans="1:15" ht="90">
       <c r="A34" s="39">
         <v>33</v>
       </c>
@@ -6926,7 +6925,7 @@
       </c>
       <c r="O34" s="24"/>
     </row>
-    <row r="35" spans="1:15" ht="137.25">
+    <row r="35" spans="1:15" ht="120">
       <c r="A35" s="39">
         <v>34</v>
       </c>
@@ -6965,7 +6964,7 @@
       </c>
       <c r="O35" s="24"/>
     </row>
-    <row r="36" spans="1:15" ht="91.5">
+    <row r="36" spans="1:15" ht="75">
       <c r="A36" s="39">
         <v>35</v>
       </c>
@@ -7004,7 +7003,7 @@
       </c>
       <c r="O36" s="24"/>
     </row>
-    <row r="37" spans="1:15" ht="106.5">
+    <row r="37" spans="1:15" ht="90">
       <c r="A37" s="39">
         <v>36</v>
       </c>
@@ -7043,7 +7042,7 @@
       </c>
       <c r="O37" s="24"/>
     </row>
-    <row r="38" spans="1:15" ht="91.5">
+    <row r="38" spans="1:15" ht="75">
       <c r="A38" s="39">
         <v>37</v>
       </c>
@@ -7082,7 +7081,7 @@
       </c>
       <c r="O38" s="24"/>
     </row>
-    <row r="39" spans="1:15" ht="106.5">
+    <row r="39" spans="1:15" ht="90">
       <c r="A39" s="39">
         <v>38</v>
       </c>
@@ -7121,7 +7120,7 @@
       </c>
       <c r="O39" s="24"/>
     </row>
-    <row r="40" spans="1:15" ht="91.5">
+    <row r="40" spans="1:15" ht="90">
       <c r="A40" s="39">
         <v>39</v>
       </c>
@@ -7160,7 +7159,7 @@
       </c>
       <c r="O40" s="24"/>
     </row>
-    <row r="41" spans="1:15" ht="76.5">
+    <row r="41" spans="1:15" ht="75">
       <c r="A41" s="39">
         <v>40</v>
       </c>
@@ -7199,7 +7198,7 @@
       </c>
       <c r="O41" s="24"/>
     </row>
-    <row r="42" spans="1:15" ht="152.25">
+    <row r="42" spans="1:15" ht="135">
       <c r="A42" s="39">
         <v>41</v>
       </c>
@@ -7238,7 +7237,7 @@
       </c>
       <c r="O42" s="24"/>
     </row>
-    <row r="43" spans="1:15" ht="167.25">
+    <row r="43" spans="1:15" ht="150">
       <c r="A43" s="39">
         <v>42</v>
       </c>
@@ -7277,7 +7276,7 @@
       </c>
       <c r="O43" s="24"/>
     </row>
-    <row r="44" spans="1:15" ht="152.25">
+    <row r="44" spans="1:15" ht="135">
       <c r="A44" s="39">
         <v>43</v>
       </c>
@@ -7316,7 +7315,7 @@
       </c>
       <c r="O44" s="24"/>
     </row>
-    <row r="45" spans="1:15" ht="121.5">
+    <row r="45" spans="1:15" ht="105">
       <c r="A45" s="39">
         <v>44</v>
       </c>
@@ -7355,7 +7354,7 @@
       </c>
       <c r="O45" s="24"/>
     </row>
-    <row r="46" spans="1:15" ht="76.5">
+    <row r="46" spans="1:15" ht="75">
       <c r="A46" s="39">
         <v>45</v>
       </c>
@@ -7462,7 +7461,7 @@
       <c r="L48" s="23"/>
       <c r="O48" s="24"/>
     </row>
-    <row r="49" spans="1:15" ht="106.5">
+    <row r="49" spans="1:15" ht="90">
       <c r="A49" s="39">
         <v>48</v>
       </c>
@@ -7497,7 +7496,7 @@
       <c r="L49" s="23"/>
       <c r="O49" s="24"/>
     </row>
-    <row r="50" spans="1:15" ht="91.5">
+    <row r="50" spans="1:15" ht="90">
       <c r="A50" s="39">
         <v>49</v>
       </c>
@@ -7530,7 +7529,7 @@
       <c r="L50" s="23"/>
       <c r="O50" s="24"/>
     </row>
-    <row r="51" spans="1:15" ht="137.25">
+    <row r="51" spans="1:15" ht="135">
       <c r="A51" s="39">
         <v>50</v>
       </c>
@@ -7563,7 +7562,7 @@
       <c r="L51" s="23"/>
       <c r="O51" s="24"/>
     </row>
-    <row r="52" spans="1:15" ht="106.5">
+    <row r="52" spans="1:15" ht="105">
       <c r="A52" s="39">
         <v>51</v>
       </c>
@@ -7600,7 +7599,7 @@
       </c>
       <c r="O52" s="24"/>
     </row>
-    <row r="53" spans="1:15" ht="60.75">
+    <row r="53" spans="1:15" ht="60">
       <c r="A53" s="39">
         <v>52</v>
       </c>
@@ -7635,7 +7634,7 @@
       <c r="L53" s="23"/>
       <c r="O53" s="24"/>
     </row>
-    <row r="54" spans="1:15" ht="121.5">
+    <row r="54" spans="1:15" ht="105">
       <c r="A54" s="39">
         <v>53</v>
       </c>
@@ -7674,7 +7673,7 @@
       </c>
       <c r="O54" s="24"/>
     </row>
-    <row r="55" spans="1:15" ht="137.25">
+    <row r="55" spans="1:15" ht="120">
       <c r="A55" s="39">
         <v>54</v>
       </c>
@@ -7713,7 +7712,7 @@
       </c>
       <c r="O55" s="24"/>
     </row>
-    <row r="56" spans="1:15" ht="137.25">
+    <row r="56" spans="1:15" ht="135">
       <c r="A56" s="39">
         <v>55</v>
       </c>
@@ -7748,7 +7747,7 @@
       <c r="L56" s="23"/>
       <c r="O56" s="24"/>
     </row>
-    <row r="57" spans="1:15" ht="106.5">
+    <row r="57" spans="1:15" ht="90">
       <c r="A57" s="39">
         <v>56</v>
       </c>
@@ -7783,7 +7782,7 @@
       <c r="L57" s="23"/>
       <c r="O57" s="24"/>
     </row>
-    <row r="58" spans="1:15" ht="106.5">
+    <row r="58" spans="1:15" ht="90">
       <c r="A58" s="39">
         <v>57</v>
       </c>
@@ -7816,7 +7815,7 @@
       <c r="L58" s="23"/>
       <c r="O58" s="24"/>
     </row>
-    <row r="59" spans="1:15" ht="121.5">
+    <row r="59" spans="1:15" ht="105">
       <c r="A59" s="39">
         <v>58</v>
       </c>
@@ -7851,7 +7850,7 @@
       <c r="L59" s="23"/>
       <c r="O59" s="24"/>
     </row>
-    <row r="60" spans="1:15" ht="106.5">
+    <row r="60" spans="1:15" ht="90">
       <c r="A60" s="39">
         <v>59</v>
       </c>
@@ -7886,7 +7885,7 @@
       <c r="L60" s="23"/>
       <c r="O60" s="24"/>
     </row>
-    <row r="61" spans="1:15" ht="91.5">
+    <row r="61" spans="1:15" ht="75">
       <c r="A61" s="39">
         <v>60</v>
       </c>
@@ -7919,7 +7918,7 @@
       <c r="L61" s="23"/>
       <c r="O61" s="24"/>
     </row>
-    <row r="62" spans="1:15" ht="106.5">
+    <row r="62" spans="1:15" ht="90">
       <c r="A62" s="39">
         <v>61</v>
       </c>
@@ -7954,7 +7953,7 @@
       <c r="L62" s="23"/>
       <c r="O62" s="24"/>
     </row>
-    <row r="63" spans="1:15" ht="121.5">
+    <row r="63" spans="1:15" ht="105">
       <c r="A63" s="39">
         <v>62</v>
       </c>
@@ -7989,7 +7988,7 @@
       <c r="L63" s="23"/>
       <c r="O63" s="24"/>
     </row>
-    <row r="64" spans="1:15" ht="260.25">
+    <row r="64" spans="1:15" ht="228">
       <c r="A64" s="39">
         <v>63</v>
       </c>
@@ -8028,7 +8027,7 @@
       </c>
       <c r="O64" s="24"/>
     </row>
-    <row r="65" spans="1:15" ht="167.25">
+    <row r="65" spans="1:15" ht="135">
       <c r="A65" s="39">
         <v>64</v>
       </c>
@@ -8067,7 +8066,7 @@
       </c>
       <c r="O65" s="24"/>
     </row>
-    <row r="66" spans="1:15" ht="115.5">
+    <row r="66" spans="1:15" ht="114">
       <c r="A66" s="39">
         <v>65</v>
       </c>
@@ -8106,7 +8105,7 @@
       </c>
       <c r="O66" s="24"/>
     </row>
-    <row r="67" spans="1:15" ht="121.5">
+    <row r="67" spans="1:15" ht="120">
       <c r="A67" s="39">
         <v>66</v>
       </c>
@@ -8141,7 +8140,7 @@
       </c>
       <c r="O67" s="24"/>
     </row>
-    <row r="68" spans="1:15" ht="91.5">
+    <row r="68" spans="1:15" ht="75">
       <c r="A68" s="39">
         <v>67</v>
       </c>
@@ -8178,7 +8177,7 @@
       </c>
       <c r="O68" s="24"/>
     </row>
-    <row r="69" spans="1:15" ht="121.5">
+    <row r="69" spans="1:15" ht="105">
       <c r="A69" s="39">
         <v>68</v>
       </c>
@@ -8213,7 +8212,7 @@
       </c>
       <c r="O69" s="24"/>
     </row>
-    <row r="70" spans="1:15" ht="167.25">
+    <row r="70" spans="1:15" ht="150">
       <c r="A70" s="39">
         <v>69</v>
       </c>
@@ -8250,7 +8249,7 @@
       </c>
       <c r="O70" s="24"/>
     </row>
-    <row r="71" spans="1:15" ht="121.5">
+    <row r="71" spans="1:15" ht="120">
       <c r="A71" s="39">
         <v>70</v>
       </c>
@@ -8287,7 +8286,7 @@
       </c>
       <c r="O71" s="24"/>
     </row>
-    <row r="72" spans="1:15" ht="137.25">
+    <row r="72" spans="1:15" ht="120">
       <c r="A72" s="39">
         <v>71</v>
       </c>
@@ -8324,7 +8323,7 @@
       </c>
       <c r="O72" s="24"/>
     </row>
-    <row r="73" spans="1:15" ht="76.5">
+    <row r="73" spans="1:15" ht="75">
       <c r="A73" s="39">
         <v>72</v>
       </c>
@@ -8363,7 +8362,7 @@
       </c>
       <c r="O73" s="24"/>
     </row>
-    <row r="74" spans="1:15" ht="152.25">
+    <row r="74" spans="1:15" ht="135">
       <c r="A74" s="39">
         <v>73</v>
       </c>
@@ -8402,7 +8401,7 @@
       </c>
       <c r="O74" s="24"/>
     </row>
-    <row r="75" spans="1:15" ht="76.5">
+    <row r="75" spans="1:15" ht="75">
       <c r="A75" s="39">
         <v>74</v>
       </c>
@@ -8439,7 +8438,7 @@
       </c>
       <c r="O75" s="24"/>
     </row>
-    <row r="76" spans="1:15" ht="244.5">
+    <row r="76" spans="1:15" ht="225">
       <c r="A76" s="39">
         <v>75</v>
       </c>
@@ -8476,7 +8475,7 @@
       </c>
       <c r="O76" s="24"/>
     </row>
-    <row r="77" spans="1:15" ht="137.25">
+    <row r="77" spans="1:15" ht="120">
       <c r="A77" s="39">
         <v>76</v>
       </c>
@@ -8513,7 +8512,7 @@
       </c>
       <c r="O77" s="24"/>
     </row>
-    <row r="78" spans="1:15" ht="76.5">
+    <row r="78" spans="1:15" ht="75">
       <c r="A78" s="39">
         <v>77</v>
       </c>
@@ -8550,7 +8549,7 @@
       </c>
       <c r="O78" s="24"/>
     </row>
-    <row r="79" spans="1:15" ht="76.5">
+    <row r="79" spans="1:15" ht="60">
       <c r="A79" s="39">
         <v>78</v>
       </c>
@@ -8585,7 +8584,7 @@
       <c r="L79" s="23"/>
       <c r="O79" s="24"/>
     </row>
-    <row r="80" spans="1:15" ht="244.5">
+    <row r="80" spans="1:15" ht="210">
       <c r="A80" s="39">
         <v>79</v>
       </c>
@@ -8622,7 +8621,7 @@
       </c>
       <c r="O80" s="24"/>
     </row>
-    <row r="81" spans="1:15" ht="106.5">
+    <row r="81" spans="1:15" ht="90">
       <c r="A81" s="39">
         <v>80</v>
       </c>
@@ -8659,7 +8658,7 @@
       </c>
       <c r="O81" s="24"/>
     </row>
-    <row r="82" spans="1:15" ht="91.5">
+    <row r="82" spans="1:15" ht="90">
       <c r="A82" s="39">
         <v>81</v>
       </c>
@@ -8696,7 +8695,7 @@
       </c>
       <c r="O82" s="24"/>
     </row>
-    <row r="83" spans="1:15" ht="152.25">
+    <row r="83" spans="1:15" ht="150">
       <c r="A83" s="39">
         <v>82</v>
       </c>
@@ -8733,7 +8732,7 @@
       </c>
       <c r="O83" s="24"/>
     </row>
-    <row r="84" spans="1:15" ht="91.5">
+    <row r="84" spans="1:15" ht="75">
       <c r="A84" s="39">
         <v>83</v>
       </c>
@@ -8770,7 +8769,7 @@
       <c r="L84" s="23"/>
       <c r="O84" s="24"/>
     </row>
-    <row r="85" spans="1:15" ht="198">
+    <row r="85" spans="1:15" ht="165">
       <c r="A85" s="39">
         <v>84</v>
       </c>
@@ -8805,7 +8804,7 @@
       <c r="L85" s="23"/>
       <c r="O85" s="24"/>
     </row>
-    <row r="86" spans="1:15" ht="106.5">
+    <row r="86" spans="1:15" ht="90">
       <c r="A86" s="39">
         <v>85</v>
       </c>
@@ -8838,7 +8837,7 @@
       <c r="L86" s="23"/>
       <c r="O86" s="24"/>
     </row>
-    <row r="87" spans="1:15" ht="91.5">
+    <row r="87" spans="1:15" ht="90">
       <c r="A87" s="39">
         <v>86</v>
       </c>
@@ -8875,7 +8874,7 @@
       </c>
       <c r="O87" s="24"/>
     </row>
-    <row r="88" spans="1:15" ht="106.5">
+    <row r="88" spans="1:15" ht="90">
       <c r="A88" s="39">
         <v>87</v>
       </c>
@@ -8912,7 +8911,7 @@
       </c>
       <c r="O88" s="24"/>
     </row>
-    <row r="89" spans="1:15" ht="60.75">
+    <row r="89" spans="1:15" ht="60">
       <c r="A89" s="39">
         <v>88</v>
       </c>
@@ -8947,7 +8946,7 @@
       <c r="L89" s="23"/>
       <c r="O89" s="24"/>
     </row>
-    <row r="90" spans="1:15" ht="91.5">
+    <row r="90" spans="1:15" ht="75">
       <c r="A90" s="39">
         <v>89</v>
       </c>
@@ -8984,7 +8983,7 @@
       </c>
       <c r="O90" s="24"/>
     </row>
-    <row r="91" spans="1:15" ht="115.5">
+    <row r="91" spans="1:15" ht="128.25">
       <c r="A91" s="39">
         <v>90</v>
       </c>
@@ -9023,7 +9022,7 @@
       </c>
       <c r="O91" s="24"/>
     </row>
-    <row r="92" spans="1:15" ht="91.5">
+    <row r="92" spans="1:15" ht="75">
       <c r="A92" s="39">
         <v>91</v>
       </c>
@@ -9060,7 +9059,7 @@
       </c>
       <c r="O92" s="24"/>
     </row>
-    <row r="93" spans="1:15" ht="106.5">
+    <row r="93" spans="1:15" ht="90">
       <c r="A93" s="39">
         <v>92</v>
       </c>
@@ -9097,7 +9096,7 @@
       </c>
       <c r="O93" s="24"/>
     </row>
-    <row r="94" spans="1:15" ht="174">
+    <row r="94" spans="1:15" ht="185.25">
       <c r="A94" s="39">
         <v>93</v>
       </c>
@@ -9134,7 +9133,7 @@
       </c>
       <c r="O94" s="24"/>
     </row>
-    <row r="95" spans="1:15" ht="106.5">
+    <row r="95" spans="1:15" ht="90">
       <c r="A95" s="39">
         <v>94</v>
       </c>
@@ -9171,7 +9170,7 @@
       </c>
       <c r="O95" s="24"/>
     </row>
-    <row r="96" spans="1:15" ht="106.5">
+    <row r="96" spans="1:15" ht="90">
       <c r="A96" s="39">
         <v>95</v>
       </c>
@@ -9208,7 +9207,7 @@
       </c>
       <c r="O96" s="24"/>
     </row>
-    <row r="97" spans="1:15" ht="106.5">
+    <row r="97" spans="1:15" ht="90">
       <c r="A97" s="39">
         <v>96</v>
       </c>
@@ -9243,7 +9242,7 @@
       <c r="L97" s="23"/>
       <c r="O97" s="24"/>
     </row>
-    <row r="98" spans="1:15" ht="106.5">
+    <row r="98" spans="1:15" ht="90">
       <c r="A98" s="39">
         <v>97</v>
       </c>
@@ -9280,7 +9279,7 @@
       </c>
       <c r="O98" s="24"/>
     </row>
-    <row r="99" spans="1:15" ht="76.5">
+    <row r="99" spans="1:15" ht="60">
       <c r="A99" s="39">
         <v>98</v>
       </c>
@@ -9317,7 +9316,7 @@
       </c>
       <c r="O99" s="24"/>
     </row>
-    <row r="100" spans="1:15" ht="76.5">
+    <row r="100" spans="1:15" ht="60">
       <c r="A100" s="39">
         <v>99</v>
       </c>
@@ -9354,7 +9353,7 @@
       </c>
       <c r="O100" s="24"/>
     </row>
-    <row r="101" spans="1:15" ht="91.5">
+    <row r="101" spans="1:15" ht="75">
       <c r="A101" s="39">
         <v>100</v>
       </c>
@@ -9393,7 +9392,7 @@
       </c>
       <c r="O101" s="24"/>
     </row>
-    <row r="102" spans="1:15" ht="76.5">
+    <row r="102" spans="1:15" ht="60">
       <c r="A102" s="39">
         <v>101</v>
       </c>
@@ -9430,7 +9429,7 @@
       </c>
       <c r="O102" s="24"/>
     </row>
-    <row r="103" spans="1:15" ht="60.75">
+    <row r="103" spans="1:15" ht="60">
       <c r="A103" s="39">
         <v>102</v>
       </c>
@@ -9467,7 +9466,7 @@
       </c>
       <c r="O103" s="24"/>
     </row>
-    <row r="104" spans="1:15" ht="76.5">
+    <row r="104" spans="1:15" ht="75">
       <c r="A104" s="39">
         <v>103</v>
       </c>
@@ -9502,7 +9501,7 @@
       <c r="L104" s="23"/>
       <c r="O104" s="24"/>
     </row>
-    <row r="105" spans="1:15" ht="106.5">
+    <row r="105" spans="1:15" ht="105">
       <c r="A105" s="39">
         <v>104</v>
       </c>
@@ -9539,7 +9538,7 @@
       </c>
       <c r="O105" s="24"/>
     </row>
-    <row r="106" spans="1:15" ht="106.5">
+    <row r="106" spans="1:15" ht="90">
       <c r="A106" s="39">
         <v>105</v>
       </c>
@@ -9576,7 +9575,7 @@
       </c>
       <c r="O106" s="24"/>
     </row>
-    <row r="107" spans="1:15" ht="76.5">
+    <row r="107" spans="1:15" ht="60">
       <c r="A107" s="39">
         <v>106</v>
       </c>
@@ -9613,7 +9612,7 @@
       </c>
       <c r="O107" s="24"/>
     </row>
-    <row r="108" spans="1:15" ht="137.25">
+    <row r="108" spans="1:15" ht="120">
       <c r="A108" s="39">
         <v>107</v>
       </c>
@@ -9650,7 +9649,7 @@
       </c>
       <c r="O108" s="24"/>
     </row>
-    <row r="109" spans="1:15" ht="106.5">
+    <row r="109" spans="1:15" ht="105">
       <c r="A109" s="39">
         <v>108</v>
       </c>
@@ -9687,7 +9686,7 @@
       </c>
       <c r="O109" s="24"/>
     </row>
-    <row r="110" spans="1:15" ht="106.5">
+    <row r="110" spans="1:15" ht="105">
       <c r="A110" s="51">
         <v>109</v>
       </c>
@@ -9724,7 +9723,7 @@
       </c>
       <c r="O110" s="24"/>
     </row>
-    <row r="111" spans="1:15" ht="60.75">
+    <row r="111" spans="1:15" ht="60">
       <c r="A111" s="59">
         <v>110</v>
       </c>
@@ -9761,7 +9760,7 @@
       </c>
       <c r="O111" s="24"/>
     </row>
-    <row r="112" spans="1:15" ht="106.5">
+    <row r="112" spans="1:15" ht="90">
       <c r="A112" s="9">
         <v>111</v>
       </c>
@@ -9800,7 +9799,7 @@
       </c>
       <c r="O112" s="24"/>
     </row>
-    <row r="113" spans="1:15" ht="106.5">
+    <row r="113" spans="1:15" ht="105">
       <c r="A113" s="54">
         <v>112</v>
       </c>
@@ -9837,7 +9836,7 @@
       </c>
       <c r="O113" s="24"/>
     </row>
-    <row r="114" spans="1:15" ht="121.5">
+    <row r="114" spans="1:15" ht="105">
       <c r="A114" s="39">
         <v>113</v>
       </c>
@@ -9909,7 +9908,7 @@
       </c>
       <c r="O115" s="24"/>
     </row>
-    <row r="116" spans="1:15" ht="137.25">
+    <row r="116" spans="1:15" ht="120">
       <c r="A116" s="39">
         <v>115</v>
       </c>
@@ -9946,7 +9945,7 @@
       </c>
       <c r="O116" s="24"/>
     </row>
-    <row r="117" spans="1:15" ht="91.5">
+    <row r="117" spans="1:15" ht="90">
       <c r="A117" s="39">
         <v>116</v>
       </c>
@@ -9981,7 +9980,7 @@
       <c r="L117" s="23"/>
       <c r="O117" s="24"/>
     </row>
-    <row r="118" spans="1:15" ht="60.75">
+    <row r="118" spans="1:15" ht="60">
       <c r="A118" s="39">
         <v>117</v>
       </c>
@@ -10018,7 +10017,7 @@
       </c>
       <c r="O118" s="24"/>
     </row>
-    <row r="119" spans="1:15" ht="60.75">
+    <row r="119" spans="1:15" ht="60">
       <c r="A119" s="39">
         <v>118</v>
       </c>
@@ -10053,7 +10052,7 @@
       <c r="L119" s="23"/>
       <c r="O119" s="24"/>
     </row>
-    <row r="120" spans="1:15" ht="60.75">
+    <row r="120" spans="1:15" ht="60">
       <c r="A120" s="39">
         <v>119</v>
       </c>
@@ -10088,7 +10087,7 @@
       <c r="L120" s="23"/>
       <c r="O120" s="24"/>
     </row>
-    <row r="121" spans="1:15" ht="91.5">
+    <row r="121" spans="1:15" ht="75">
       <c r="A121" s="39">
         <v>120</v>
       </c>
@@ -10125,7 +10124,7 @@
       <c r="L121" s="23"/>
       <c r="O121" s="24"/>
     </row>
-    <row r="122" spans="1:15" ht="121.5">
+    <row r="122" spans="1:15" ht="105">
       <c r="A122" s="39">
         <v>121</v>
       </c>
@@ -10160,7 +10159,7 @@
       <c r="L122" s="23"/>
       <c r="O122" s="24"/>
     </row>
-    <row r="123" spans="1:15" ht="106.5">
+    <row r="123" spans="1:15" ht="105">
       <c r="A123" s="39">
         <v>122</v>
       </c>
@@ -10195,7 +10194,7 @@
       <c r="L123" s="23"/>
       <c r="O123" s="24"/>
     </row>
-    <row r="124" spans="1:15" ht="106.5">
+    <row r="124" spans="1:15" ht="90">
       <c r="A124" s="39">
         <v>123</v>
       </c>
@@ -10269,7 +10268,7 @@
       </c>
       <c r="O125" s="24"/>
     </row>
-    <row r="126" spans="1:15" ht="60.75">
+    <row r="126" spans="1:15" ht="60">
       <c r="A126" s="39">
         <v>125</v>
       </c>
@@ -10304,7 +10303,7 @@
       <c r="L126" s="23"/>
       <c r="O126" s="24"/>
     </row>
-    <row r="127" spans="1:15" ht="91.5">
+    <row r="127" spans="1:15" ht="90">
       <c r="A127" s="39">
         <v>126</v>
       </c>
@@ -10339,7 +10338,7 @@
       <c r="L127" s="23"/>
       <c r="O127" s="24"/>
     </row>
-    <row r="128" spans="1:15" ht="106.5">
+    <row r="128" spans="1:15" ht="90">
       <c r="A128" s="39">
         <v>127</v>
       </c>
@@ -10373,7 +10372,7 @@
       </c>
       <c r="L128" s="23"/>
     </row>
-    <row r="129" spans="1:12" ht="183">
+    <row r="129" spans="1:12" ht="165">
       <c r="A129" s="39">
         <v>128</v>
       </c>
@@ -10409,7 +10408,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="76.5">
+    <row r="130" spans="1:12" ht="60">
       <c r="A130" s="39">
         <v>129</v>
       </c>
@@ -10443,7 +10442,7 @@
       </c>
       <c r="L130" s="23"/>
     </row>
-    <row r="131" spans="1:12" ht="76.5">
+    <row r="131" spans="1:12" ht="60">
       <c r="A131" s="39">
         <v>130</v>
       </c>
@@ -10477,7 +10476,7 @@
       </c>
       <c r="L131" s="23"/>
     </row>
-    <row r="132" spans="1:12" ht="106.5">
+    <row r="132" spans="1:12" ht="90">
       <c r="A132" s="39">
         <v>131</v>
       </c>
@@ -10511,7 +10510,7 @@
       </c>
       <c r="L132" s="23"/>
     </row>
-    <row r="133" spans="1:12" ht="76.5">
+    <row r="133" spans="1:12" ht="75">
       <c r="A133" s="39">
         <v>132</v>
       </c>
@@ -10546,19 +10545,19 @@
       <c r="L133" s="23"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O133" xr:uid="{E2369B40-7046-473B-B809-8561F6CA1BF7}"/>
+  <autoFilter ref="A1:O133"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E7C3B22-150D-446F-B3CE-B3453ED458CB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E354"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="41.5703125" customWidth="1"/>
-    <col min="4" max="4" width="197.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.625" customWidth="1"/>
+    <col min="4" max="4" width="197.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -10816,7 +10815,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="29.25">
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>4</v>
       </c>
@@ -10833,7 +10832,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="29.25">
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>4</v>
       </c>
@@ -10867,7 +10866,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="29.25">
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>4</v>
       </c>
@@ -10901,7 +10900,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="43.5">
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>4</v>
       </c>
@@ -10918,7 +10917,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="72.75">
+    <row r="22" spans="1:5">
       <c r="A22">
         <v>4</v>
       </c>
@@ -11037,7 +11036,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="29.25">
+    <row r="29" spans="1:5">
       <c r="A29">
         <v>7</v>
       </c>
@@ -11054,7 +11053,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="29.25">
+    <row r="30" spans="1:5">
       <c r="A30">
         <v>7</v>
       </c>
@@ -12193,7 +12192,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="29.25">
+    <row r="97" spans="1:5">
       <c r="A97">
         <v>47</v>
       </c>
@@ -12210,7 +12209,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="43.5">
+    <row r="98" spans="1:5">
       <c r="A98">
         <v>47</v>
       </c>
@@ -13991,6 +13990,9 @@
       <c r="D202" t="s">
         <v>1150</v>
       </c>
+      <c r="E202" t="s">
+        <v>436</v>
+      </c>
     </row>
     <row r="203" spans="1:5">
       <c r="A203">
@@ -16577,21 +16579,21 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E354" xr:uid="{6E7C3B22-150D-446F-B3CE-B3453ED458CB}"/>
+  <autoFilter ref="A1:E354"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4284D02-A19C-4F07-90D9-B9B051A7FA8A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="57.75">
+    <row r="1" spans="1:2" ht="57">
       <c r="A1" t="s">
         <v>17</v>
       </c>
@@ -16599,7 +16601,7 @@
         <v>1460</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="101.25">
+    <row r="2" spans="1:2" ht="99.75">
       <c r="A2" t="s">
         <v>317</v>
       </c>
@@ -16607,7 +16609,7 @@
         <v>1461</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="115.5">
+    <row r="3" spans="1:2" ht="114">
       <c r="A3" t="s">
         <v>550</v>
       </c>
@@ -16615,7 +16617,7 @@
         <v>1462</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="115.5">
+    <row r="4" spans="1:2" ht="114">
       <c r="A4" t="s">
         <v>649</v>
       </c>
@@ -16629,15 +16631,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100506FD4652602C740A483E9D3DF6A153B" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3ae790dad332779219ad741447ce1449">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1aa39b8c-19b3-4ca5-9ada-a1970df5e875" xmlns:ns3="a9968193-2d77-4b73-840a-26fc33ae728b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bceb73c01ba1e25437ffc1b7a59fee3b" ns2:_="" ns3:_="">
     <xsd:import namespace="1aa39b8c-19b3-4ca5-9ada-a1970df5e875"/>
@@ -16892,6 +16885,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -16904,13 +16906,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2FD2D9B6-68AB-4A59-BCBA-EC7E4F0054ED}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BFC49B3-58DA-49B8-A3A9-093E89BDDE73}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="1aa39b8c-19b3-4ca5-9ada-a1970df5e875"/>
+    <ds:schemaRef ds:uri="a9968193-2d77-4b73-840a-26fc33ae728b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BFC49B3-58DA-49B8-A3A9-093E89BDDE73}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2FD2D9B6-68AB-4A59-BCBA-EC7E4F0054ED}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9DFCD87-1494-4CF4-9D60-842DA5D97CB7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9DFCD87-1494-4CF4-9D60-842DA5D97CB7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1aa39b8c-19b3-4ca5-9ada-a1970df5e875"/>
+    <ds:schemaRef ds:uri="a9968193-2d77-4b73-840a-26fc33ae728b"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/backend/estrutura_pdm/data/xl/dados_metas_atualizados_v2.xlsx
+++ b/backend/estrutura_pdm/data/xl/dados_metas_atualizados_v2.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2749" uniqueCount="1464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2749" uniqueCount="1465">
   <si>
     <t>Número da Meta</t>
   </si>
@@ -4536,6 +4536,9 @@
   </si>
   <si>
     <t>O eixo Capital do Futuro reúne metas voltadas à modernização da administração pública, à transformação digital e ao aperfeiçoamento da relação entre governo e cidadão. Trata do compromisso com a transparência e da participação das pessoas como protagonistas dos processos decisórios.</t>
+  </si>
+  <si>
+    <t>129.04</t>
   </si>
 </sst>
 </file>
@@ -5599,7 +5602,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -16365,7 +16368,7 @@
         <v>1428</v>
       </c>
       <c r="C342" t="s">
-        <v>1433</v>
+        <v>1464</v>
       </c>
       <c r="D342" t="s">
         <v>1435</v>
@@ -16631,6 +16634,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100506FD4652602C740A483E9D3DF6A153B" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3ae790dad332779219ad741447ce1449">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1aa39b8c-19b3-4ca5-9ada-a1970df5e875" xmlns:ns3="a9968193-2d77-4b73-840a-26fc33ae728b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bceb73c01ba1e25437ffc1b7a59fee3b" ns2:_="" ns3:_="">
     <xsd:import namespace="1aa39b8c-19b3-4ca5-9ada-a1970df5e875"/>
@@ -16885,15 +16897,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -16906,6 +16909,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2FD2D9B6-68AB-4A59-BCBA-EC7E4F0054ED}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BFC49B3-58DA-49B8-A3A9-093E89BDDE73}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -16924,14 +16935,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2FD2D9B6-68AB-4A59-BCBA-EC7E4F0054ED}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9DFCD87-1494-4CF4-9D60-842DA5D97CB7}">
   <ds:schemaRefs>
